--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,232 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136933010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136950253</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102705</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Korsåmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>580972</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6976164</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Signe Jönsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950253</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136950521</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102705</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Korsåmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>580981</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6976180</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Signe Jönsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950521</t>
         </is>
       </c>
     </row>
@@ -894,6 +1120,8 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102705</v>
+        <v>102711</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102711</v>
+        <v>102713</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102713</v>
+        <v>102714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102714</v>
+        <v>102720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102720</v>
+        <v>102724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102724</v>
+        <v>102726</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102726</v>
+        <v>102728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102728</v>
+        <v>102741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102741</v>
+        <v>102743</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102743</v>
+        <v>102746</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102746</v>
+        <v>102761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102761</v>
+        <v>102762</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102762</v>
+        <v>102767</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102767</v>
+        <v>102770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102770</v>
+        <v>102776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102776</v>
+        <v>102788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102788</v>
+        <v>102789</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102789</v>
+        <v>102792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102792</v>
+        <v>102793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24159-2025 artfynd.xlsx
+++ b/artfynd/A 24159-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136933009</v>
       </c>
       <c r="B2" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136933010</v>
       </c>
       <c r="B3" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136950253</v>
       </c>
       <c r="B4" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136950521</v>
       </c>
       <c r="B5" t="n">
-        <v>102793</v>
+        <v>102796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
